--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 31,08,26 млрсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 31,08,26 млрсч ост зпф.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428BC2D0-1029-4B6E-AF2A-142C10D600C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F74B4C4-39B6-45CC-8CDA-A015CB5F6DF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -68,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -164,6 +169,12 @@
   </si>
   <si>
     <t>7216 СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>07,09,</t>
   </si>
 </sst>
 </file>
@@ -760,46 +771,46 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
@@ -837,40 +848,42 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q4" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
@@ -937,7 +950,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -980,7 +993,7 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="4">
         <f>SUM(AD6:AD500)</f>
-        <v>197.45</v>
+        <v>198.5</v>
       </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
@@ -1004,10 +1017,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C6" s="1">
         <v>92</v>
@@ -1026,7 +1039,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1">
@@ -1080,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="AC6" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD6" s="1">
         <f>G6*Q6</f>
@@ -1108,10 +1121,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C7" s="1">
         <v>196.68199999999999</v>
@@ -1128,7 +1141,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1180,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="AC7" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD7" s="1">
         <f>G7*Q7</f>
@@ -1208,10 +1221,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1">
         <v>95.147999999999996</v>
@@ -1228,7 +1241,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1280,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="AC8" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD8" s="1">
         <f>G8*Q8</f>
@@ -1308,10 +1321,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1324,7 +1337,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -1376,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="AC9" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD9" s="7"/>
       <c r="AE9" s="1"/>
@@ -1401,10 +1414,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1">
         <v>329</v>
@@ -1423,7 +1436,7 @@
         <v>120</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1441,12 +1454,11 @@
         <v>21.6</v>
       </c>
       <c r="Q10" s="5">
-        <f>15*P10-O10-F10</f>
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="R10" s="1">
         <f t="shared" si="4"/>
-        <v>14.999999999999998</v>
+        <v>15.138888888888888</v>
       </c>
       <c r="S10" s="1">
         <f t="shared" si="5"/>
@@ -1482,7 +1494,7 @@
       <c r="AC10" s="1"/>
       <c r="AD10" s="1">
         <f t="shared" ref="AD10:AD16" si="6">G10*Q10</f>
-        <v>32.1</v>
+        <v>33</v>
       </c>
       <c r="AE10" s="1"/>
       <c r="AF10" s="1"/>
@@ -1506,10 +1518,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1">
         <v>95</v>
@@ -1528,7 +1540,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1546,12 +1558,11 @@
         <v>9</v>
       </c>
       <c r="Q11" s="5">
-        <f t="shared" ref="Q11:Q14" si="7">15*P11-O11-F11</f>
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>15.555555555555555</v>
       </c>
       <c r="S11" s="1">
         <f t="shared" si="5"/>
@@ -1587,7 +1598,7 @@
       <c r="AC11" s="1"/>
       <c r="AD11" s="1">
         <f t="shared" si="6"/>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
@@ -1611,10 +1622,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1">
         <v>376</v>
@@ -1633,7 +1644,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1651,12 +1662,11 @@
         <v>24.6</v>
       </c>
       <c r="Q12" s="5">
-        <f t="shared" si="7"/>
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14.918699186991869</v>
       </c>
       <c r="S12" s="1">
         <f t="shared" si="5"/>
@@ -1692,7 +1702,7 @@
       <c r="AC12" s="1"/>
       <c r="AD12" s="1">
         <f t="shared" si="6"/>
-        <v>42.699999999999996</v>
+        <v>42</v>
       </c>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
@@ -1716,10 +1726,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1">
         <v>58</v>
@@ -1738,7 +1748,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1758,12 +1768,11 @@
         <v>6.8</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" si="7"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14.852941176470589</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="5"/>
@@ -1799,7 +1808,7 @@
       <c r="AC13" s="1"/>
       <c r="AD13" s="1">
         <f t="shared" si="6"/>
-        <v>9.2999999999999989</v>
+        <v>9</v>
       </c>
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
@@ -1823,10 +1832,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1">
         <v>290</v>
@@ -1845,7 +1854,7 @@
         <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1865,12 +1874,11 @@
         <v>29.2</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" si="7"/>
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14.965753424657535</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="5"/>
@@ -1906,7 +1914,7 @@
       <c r="AC14" s="1"/>
       <c r="AD14" s="1">
         <f t="shared" si="6"/>
-        <v>87.85</v>
+        <v>87.5</v>
       </c>
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
@@ -1930,10 +1938,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="1">
         <v>35</v>
@@ -1954,7 +1962,7 @@
         <v>120</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -2008,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD15" s="1">
         <f t="shared" si="6"/>
@@ -2036,10 +2044,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1">
         <v>276</v>
@@ -2058,7 +2066,7 @@
         <v>180</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2112,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="AC16" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" si="6"/>
